--- a/crates/xlstream-eval/tests/fixtures/statistical/skew_kurt.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/statistical/skew_kurt.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Symmetric</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Mixed</t>
   </si>
   <si>
-    <t xml:space="preserve">Error</t>
+    <t xml:space="preserve">WithErr</t>
   </si>
   <si>
     <t xml:space="preserve">Small</t>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool</t>
   </si>
   <si>
     <t xml:space="preserve">XS</t>
@@ -132,11 +135,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -417,9 +416,8 @@
       <c r="E3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="0" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
+      <c r="F3" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="G3" s="0" t="n">
         <v>20</v>
@@ -452,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" s="0" t="n">
         <v>30</v>
@@ -478,12 +476,8 @@
       <c r="D5" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>5</v>
+      <c r="E5" s="0" t="s">
+        <v>11</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>8</v>
@@ -592,24 +586,24 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J16" s="0" t="n">
         <f aca="false">SKEW(E2:E7)</f>
-        <v>0.541387050951085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J17" s="0" t="n">
         <f aca="false">KURT(E2:E7)</f>
-        <v>-1.4878892733564</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J18" s="0" t="e">
-        <f aca="false">SKEW(F2:F5)</f>
+        <f aca="false">SKEW(1, NA(), 3, 5)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J19" s="0" t="e">
-        <f aca="false">KURT(F2:F5)</f>
+        <f aca="false">KURT(1, NA(), 3, 5, 7)</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -664,7 +658,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/crates/xlstream-eval/tests/fixtures/statistical/skew_kurt.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/statistical/skew_kurt.xlsx
@@ -1,35 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason/Projects/xlstream-fix-conformance/crates/xlstream-eval/tests/fixtures/statistical/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_44540FEF8B9CD528F1F643D4261012548D0A5CAB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>Symmetric</t>
+  </si>
+  <si>
+    <t>RightSkew</t>
+  </si>
+  <si>
+    <t>LeftSkew</t>
+  </si>
+  <si>
+    <t>Same</t>
+  </si>
+  <si>
+    <t>Mixed</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Pair</t>
+  </si>
+  <si>
+    <t>Big</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +106,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,352 +408,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Symmetric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>RightSkew</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LeftSkew</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Pair</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Big</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
         <f>SKEW(A2:A6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>97</v>
       </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F3">
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="e">
         <f>NA()</f>
-        <v/>
-      </c>
-      <c r="G3" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="G3">
         <v>20</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>4</v>
       </c>
       <c r="J3">
         <f>SKEW(B2:B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+        <v>2.2323959116364582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>98</v>
       </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>30</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>6</v>
       </c>
       <c r="J4">
         <f>SKEW(C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+        <v>-2.2323959116364578</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>99</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>8</v>
       </c>
       <c r="J5">
         <f>SKEW(I2:I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>100</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
         <f>_xlfn.SKEW.P(A2:A6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E7">
         <v>7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>12</v>
       </c>
       <c r="J7">
         <f>_xlfn.SKEW.P(B2:B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="I8" t="n">
+        <v>1.4975367033335201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I8">
         <v>14</v>
       </c>
       <c r="J8">
         <f>KURT(A2:A6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="I9" t="n">
+        <v>-1.1999999999999984</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I9">
         <v>16</v>
       </c>
       <c r="J9">
         <f>KURT(B2:B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="I10" t="n">
+        <v>4.9868659572006564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I10">
         <v>18</v>
       </c>
       <c r="J10">
         <f>KURT(I2:I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="I11" t="n">
+        <v>-1.2000000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I11">
         <v>20</v>
       </c>
       <c r="J11">
         <f>SKEW(G2:G4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J12" t="e">
         <f>SKEW(H2:H3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="J13">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J13" t="e">
         <f>_xlfn.SKEW.P(H2:H3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J14">
         <f>KURT(A2:A5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="J15">
+        <v>-1.1999999999999975</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J15" t="e">
         <f>KURT(G2:G4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="J16">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J16" t="e">
         <f>SKEW(D2:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="J17">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J17" t="e">
         <f>KURT(D2:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J18">
         <f>SKEW(E2:E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J19">
         <f>KURT(E2:E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="J20">
+        <v>-1.1999999999999975</v>
+      </c>
+    </row>
+    <row r="20" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J20" t="e">
         <f>SKEW(F2:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="J21">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J21" t="e">
         <f>KURT(F2:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="J22">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J22" t="str">
         <f>IF(SKEW(B2:B6)&gt;0,"right","left")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="J23">
+        <v>right</v>
+      </c>
+    </row>
+    <row r="23" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J23" t="str">
         <f>IFERROR(KURT(G2:G4),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
+        <v>n/a</v>
+      </c>
+    </row>
+    <row r="24" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J24">
         <f>SKEW(Sheet2!A2:A6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J25">
         <f>KURT(Sheet2!A2:A6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
+        <v>-1.1999999999999984</v>
+      </c>
+    </row>
+    <row r="26" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J26">
         <f>SKEW(A2:A6)+KURT(A2:A6)</f>
-        <v/>
+        <v>-1.1999999999999984</v>
       </c>
     </row>
   </sheetData>
@@ -763,43 +736,37 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>30</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>40</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>50</v>
       </c>
     </row>
